--- a/docs/tooltip-inventory.xlsx
+++ b/docs/tooltip-inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="Ra6ac66f1c18d41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R462545faa7364cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R9d7e632613d44ddf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R927196b73f9c4aef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2324,7 +2324,7 @@
         <x:v>Checkbox</x:v>
       </x:c>
       <x:c r="D92" s="10" t="str">
-        <x:v>Use Column Gutters in InDesign</x:v>
+        <x:v>Use Column Gutter in InDesign</x:v>
       </x:c>
       <x:c r="E92" s="10" t="str">
         <x:v>Applies the calculated Column Gutter to InDesign’s Margins and Columns settings. It does not change Emetric’s grid calculations.</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>0.42.0-alpha.18</x:v>
+        <x:v>0.42.0-alpha.19</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3565,7 +3565,7 @@
         <x:v>Source inventory</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>0.42.0-alpha.17</x:v>
+        <x:v>0.42.0-alpha.18</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3597,7 +3597,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>2026-07-15 14:07</x:v>
+        <x:v>2026-07-15 14:25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/tooltip-inventory.xlsx
+++ b/docs/tooltip-inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R9d7e632613d44ddf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R927196b73f9c4aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R0754e940a5344afd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rc294cd68bc034790"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1044,13 +1044,13 @@
         <x:v>Ratio field</x:v>
       </x:c>
       <x:c r="D36" s="10" t="str">
-        <x:v>Metrics : Leading — first value</x:v>
+        <x:v>Metrics &amp; Leading Ratio — first value</x:v>
       </x:c>
       <x:c r="E36" s="10" t="str">
+        <x:v>First value in the Metrics &amp; Leading Ratio.</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="str">
         <x:v>First value in the Metrics to Leading ratio.</x:v>
-      </x:c>
-      <x:c r="F36" s="10" t="str">
-        <x:v>[Empty]</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
         <x:v>Applied from latest suggestion.</x:v>
@@ -1067,13 +1067,13 @@
         <x:v>Ratio field</x:v>
       </x:c>
       <x:c r="D37" s="10" t="str">
-        <x:v>Metrics : Leading — second value</x:v>
+        <x:v>Metrics &amp; Leading Ratio — second value</x:v>
       </x:c>
       <x:c r="E37" s="10" t="str">
+        <x:v>Second value in the Metrics &amp; Leading Ratio.</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="str">
         <x:v>Second value in the Metrics to Leading ratio.</x:v>
-      </x:c>
-      <x:c r="F37" s="10" t="str">
-        <x:v>[Empty]</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
         <x:v>Applied from latest suggestion.</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>0.42.0-alpha.19</x:v>
+        <x:v>0.42.0-alpha.20</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3565,7 +3565,7 @@
         <x:v>Source inventory</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>0.42.0-alpha.18</x:v>
+        <x:v>0.42.0-alpha.20</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3597,7 +3597,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>2026-07-15 14:25</x:v>
+        <x:v>2026-07-15 14:35</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/tooltip-inventory.xlsx
+++ b/docs/tooltip-inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R0754e940a5344afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rc294cd68bc034790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R4f9b9e30e3664706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rb4cff4bcb599456d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3557,7 +3557,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>0.42.0-alpha.20</x:v>
+        <x:v>0.42.0-alpha.21</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3565,7 +3565,7 @@
         <x:v>Source inventory</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>0.42.0-alpha.20</x:v>
+        <x:v>0.42.0-alpha.21</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3598,6 +3598,22 @@
       </x:c>
       <x:c r="B6" t="str">
         <x:v>2026-07-15 14:35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Change</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Placeholder Text uses [Basic Paragraph]; Emetric Information renamed to Emetric Data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Change</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Layers are created only when corresponding outputs are selected.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/tooltip-inventory.xlsx
+++ b/docs/tooltip-inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R4f9b9e30e3664706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rb4cff4bcb599456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="Racf525d1e0664e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rf569903c8bfb4f61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1044,7 +1044,7 @@
         <x:v>Ratio field</x:v>
       </x:c>
       <x:c r="D36" s="10" t="str">
-        <x:v>Metrics &amp; Leading Ratio — first value</x:v>
+        <x:v>M &amp; L Ratio — first value</x:v>
       </x:c>
       <x:c r="E36" s="10" t="str">
         <x:v>First value in the Metrics &amp; Leading Ratio.</x:v>
@@ -1067,7 +1067,7 @@
         <x:v>Ratio field</x:v>
       </x:c>
       <x:c r="D37" s="10" t="str">
-        <x:v>Metrics &amp; Leading Ratio — second value</x:v>
+        <x:v>M &amp; L Ratio — second value</x:v>
       </x:c>
       <x:c r="E37" s="10" t="str">
         <x:v>Second value in the Metrics &amp; Leading Ratio.</x:v>
@@ -3557,7 +3557,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>0.42.0-alpha.21</x:v>
+        <x:v>0.42.0-alpha.23</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3565,7 +3565,7 @@
         <x:v>Source inventory</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>0.42.0-alpha.21</x:v>
+        <x:v>0.42.0-alpha.23</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3597,7 +3597,7 @@
         <x:v>Generated</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>2026-07-15 14:35</x:v>
+        <x:v>2026-07-15 15:54</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3605,7 +3605,7 @@
         <x:v>Change</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Placeholder Text uses [Basic Paragraph]; Emetric Information renamed to Emetric Data.</x:v>
+        <x:v>[Basic Paragraph] is set to Align Left for Placeholder Text output.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3613,7 +3613,7 @@
         <x:v>Change</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Layers are created only when corresponding outputs are selected.</x:v>
+        <x:v>Visible label shortened to M &amp; L Ratio while retaining Metrics &amp; Leading Ratio tooltips.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/tooltip-inventory.xlsx
+++ b/docs/tooltip-inventory.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="Racf525d1e0664e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rf569903c8bfb4f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooltip Inventory" sheetId="1" r:id="R95154478f7a14f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R63ae16d8de164473"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3557,7 +3557,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>0.42.0-alpha.23</x:v>
+        <x:v>0.42.0-alpha.24</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3565,7 +3565,7 @@
         <x:v>Source inventory</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>0.42.0-alpha.23</x:v>
+        <x:v>0.42.0-alpha.24</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3605,7 +3605,7 @@
         <x:v>Change</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>[Basic Paragraph] is set to Align Left for Placeholder Text output.</x:v>
+        <x:v>Selected font output scales to the active Vertical Grid Alignment metric when using non-font Metric Sources.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3613,7 +3613,7 @@
         <x:v>Change</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Visible label shortened to M &amp; L Ratio while retaining Metrics &amp; Leading Ratio tooltips.</x:v>
+        <x:v>Tooltip text is unchanged from alpha.23; inventory version updated for alpha.24.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
